--- a/Capstone/Fase 2/Evidencias/Historias Usuario.xlsx
+++ b/Capstone/Fase 2/Evidencias/Historias Usuario.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ym\Proyecto-Yourmeds\Capstone\Fase 2\Evidencias\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080F2A00-FDCD-47C8-BA75-30896854B4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="630" yWindow="2955" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Historia de usuario" sheetId="1" r:id="rId4"/>
+    <sheet name="Historia de usuario" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="DN9rCYs9SJqnN4sKg4+HdfGn7hkQCmRG1friUSe9H1s="/>
@@ -159,103 +168,127 @@
     <t>HU12</t>
   </si>
   <si>
-    <t>E5</t>
-  </si>
-  <si>
-    <t>Como usuario quiero llevar un registro historico de las alarmas personales</t>
-  </si>
-  <si>
-    <t>Dado que el usuario cuenta con tiempo utilizando, registrando alarmas, el sistema debe mostrar el historial de los medicamentos</t>
+    <t>Como usuario quiero cerrar sesión en la interfaz principal de la aplicación</t>
+  </si>
+  <si>
+    <t>Dado que el usuario está logueado en la aplicación, el sistema debe tener un botón para cerrar sesión</t>
+  </si>
+  <si>
+    <t>Baja</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <color theme="1"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6FA8DC"/>
-        <bgColor rgb="FF6FA8DC"/>
+        <fgColor rgb="FF217BFF"/>
+        <bgColor rgb="FF6D9EEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC9DAF8"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor rgb="FFC9DAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -445,23 +478,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.71"/>
-    <col customWidth="1" min="2" max="2" width="10.0"/>
-    <col customWidth="1" min="3" max="3" width="54.71"/>
-    <col customWidth="1" min="4" max="4" width="46.43"/>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="54.7109375" customWidth="1"/>
+    <col min="4" max="4" width="46.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,7 +517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -498,10 +534,10 @@
         <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -518,10 +554,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="2">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -538,10 +574,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
@@ -558,10 +594,10 @@
         <v>22</v>
       </c>
       <c r="F5" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -578,10 +614,10 @@
         <v>10</v>
       </c>
       <c r="F6" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -598,10 +634,10 @@
         <v>29</v>
       </c>
       <c r="F7" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
@@ -618,10 +654,10 @@
         <v>10</v>
       </c>
       <c r="F8" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
@@ -638,10 +674,10 @@
         <v>29</v>
       </c>
       <c r="F9" s="2">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>37</v>
       </c>
@@ -658,10 +694,10 @@
         <v>10</v>
       </c>
       <c r="F10" s="2">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>40</v>
       </c>
@@ -678,10 +714,10 @@
         <v>10</v>
       </c>
       <c r="F11" s="2">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
@@ -698,30 +734,30 @@
         <v>10</v>
       </c>
       <c r="F12" s="2">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="13" ht="57.0" customHeight="1">
-      <c r="A13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="2">
-        <v>5.0</v>
+      <c r="F13" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Capstone/Fase 2/Evidencias/Historias Usuario.xlsx
+++ b/Capstone/Fase 2/Evidencias/Historias Usuario.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ym\Proyecto-Yourmeds\Capstone\Fase 2\Evidencias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080F2A00-FDCD-47C8-BA75-30896854B4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F02C9C1-4741-4735-8BB3-6907792C45FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="2955" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Historia de usuario" sheetId="1" r:id="rId1"/>
@@ -66,18 +66,12 @@
     <t>Como usuario quiero iniciar sesión con mi correo y contraseña para acceder a mis alarmas.</t>
   </si>
   <si>
-    <t>Dado que ingreso credenciales correctas, cuando presiono “Iniciar sesión”, entonces puedo acceder al sistema.</t>
-  </si>
-  <si>
     <t>HU3</t>
   </si>
   <si>
     <t>E3</t>
   </si>
   <si>
-    <t>Como usuario quiero registrar mis alarmas con nombre de medicamento, dosis y descripción.</t>
-  </si>
-  <si>
     <t>Dado que completo el formulario, cuando presiono “Guardar”, la alarma se almacena correctamente.</t>
   </si>
   <si>
@@ -87,33 +81,18 @@
     <t>E2</t>
   </si>
   <si>
-    <t>Como usuario quiero registrar un grupo de forma personal o compartido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dado que el usuario escoge una de las opciones, el sistema arrojará el registro del grupo con los datos correspondiente. </t>
-  </si>
-  <si>
     <t>Muy Alta</t>
   </si>
   <si>
     <t>HU5</t>
   </si>
   <si>
-    <t>Como usuario quiero editar o eliminar una alarma para actualizar mis recordatorios.</t>
-  </si>
-  <si>
     <t>Dado que selecciono una alarma, puedo modificarla o eliminarla correctamente.</t>
   </si>
   <si>
     <t>HU6</t>
   </si>
   <si>
-    <t>Como usuario quiero editar o eliminar un grupo para actualizar mis listados.</t>
-  </si>
-  <si>
-    <t>Dado que selecciono un grupo, puedo modificarla o eliminarla correctamente.</t>
-  </si>
-  <si>
     <t>Media</t>
   </si>
   <si>
@@ -126,52 +105,73 @@
     <t>Como usuario quiero recibir notificaciones automáticas cuando sea hora de tomar mi medicamento.</t>
   </si>
   <si>
-    <t>Dado que llega la hora programada, el sistema muestra una notificación.</t>
-  </si>
-  <si>
     <t>HU8</t>
   </si>
   <si>
-    <t>Como usuario quiero compartir mis alarmas con familiares o cuidadores.</t>
-  </si>
-  <si>
-    <t>Dado que elijo un grupo o usuario, el sistema comparte las alarmas correspondientes.</t>
-  </si>
-  <si>
     <t>HU9</t>
   </si>
   <si>
-    <t>Como usuario quiero que mi password sea encriptada en el sistema por seguridad</t>
-  </si>
-  <si>
-    <t>Dado que el usuario registre sus datos, el sistema encripta el password para alamacenarlo en la base de datos.</t>
-  </si>
-  <si>
     <t>HU10</t>
   </si>
   <si>
-    <t>Como usuario quiero usar el sistema con token para mayor seguridad</t>
-  </si>
-  <si>
-    <t>Dado que el usuario ingrese sus datos y se loguea en la aplicación, el sistema devolverá su token correspondiente que durará 24hrs para validar al usuario en el sistema.</t>
-  </si>
-  <si>
     <t>HU11</t>
   </si>
   <si>
-    <t>Como usuario quiero visualizar los grupos con sus respectivas alarmas</t>
-  </si>
-  <si>
-    <t>Dado que el usuario contiene grupos y alarmas creadas, el sistema debe mostrar toda la información relacionada al usuario como grupo personal y grupos compartidos</t>
+    <t>Dado que ingreso credenciales correctas, cuando presiono “Iniciar sesión”, puedo acceder al sistema.</t>
+  </si>
+  <si>
+    <t>Como usuario quiero registrar mis alarmas indicando medicamento, horario y cantidad.</t>
+  </si>
+  <si>
+    <t>Como usuario quiero registrar un grupo de forma personal o compartido.</t>
+  </si>
+  <si>
+    <t>Dado que selecciono un tipo de grupo y completo los campos, el sistema crea el grupo correctamente.</t>
+  </si>
+  <si>
+    <t>Como usuario quiero editar o eliminar una alarma.</t>
+  </si>
+  <si>
+    <t>Como usuario quiero editar o eliminar un grupo.</t>
+  </si>
+  <si>
+    <t>Dado que selecciono un grupo, puedo modificarlo o eliminarlo correctamente.</t>
+  </si>
+  <si>
+    <t>Dado que llega la hora programada, el sistema despliega una notificación.</t>
+  </si>
+  <si>
+    <t>Como usuario quiero agregar otros usuarios a mis grupos compartidos para que puedan visualizar las alarmas asociadas.</t>
+  </si>
+  <si>
+    <t>Dado que selecciono un usuario para agregar, cuando lo incorporo al grupo compartido, éste puede visualizar las alarmas del grupo.</t>
+  </si>
+  <si>
+    <t>Como usuario quiero que mi password sea encriptada en el sistema para seguridad.</t>
+  </si>
+  <si>
+    <t>Dado que ingreso mis datos, el password se almacena encriptado en la base de datos.</t>
+  </si>
+  <si>
+    <t>Como usuario quiero usar el sistema con token para mayor seguridad.</t>
+  </si>
+  <si>
+    <t>Dado que me logueo, recibo un token válido por 24h que permite validar mis acciones.</t>
+  </si>
+  <si>
+    <t>Como usuario quiero visualizar los grupos con sus respectivas alarmas.</t>
+  </si>
+  <si>
+    <t>Dado que tengo grupos y alarmas creadas, el sistema debe mostrar toda la información asociada.</t>
   </si>
   <si>
     <t>HU12</t>
   </si>
   <si>
-    <t>Como usuario quiero cerrar sesión en la interfaz principal de la aplicación</t>
-  </si>
-  <si>
-    <t>Dado que el usuario está logueado en la aplicación, el sistema debe tener un botón para cerrar sesión</t>
+    <t>Como usuario quiero cerrar sesión en la app.</t>
+  </si>
+  <si>
+    <t>Dado que estoy logueado, el sistema debe permitir cerrar sesión mediante un botón.</t>
   </si>
   <si>
     <t>Baja</t>
@@ -181,7 +181,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,20 +193,28 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -217,18 +225,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF217BFF"/>
         <bgColor rgb="FF6D9EEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor rgb="FFC9DAF8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -259,16 +255,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,7 +494,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -517,247 +523,264 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="F5" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F12" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="7">
         <v>2</v>
       </c>
     </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
+    </row>
+    <row r="17" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="3:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+    </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>